--- a/testing/Manual_Test_Cases.xlsx
+++ b/testing/Manual_Test_Cases.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual Test Cases'!$A$1:$M$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual Test Cases'!$A$1:$M$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1337,239 +1337,238 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>View user details from the admin list</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>At least one user exists</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1. Go to Admin page
+2. Click the View (eye) action on a user</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>User Details page opens showing name, email, role, contact, user ID, created/updated dates and the role's effective permissions. User is NOT logged out or sent to the login page</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC-AM-007</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Admin Management</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>View details of a doctor's linked login account</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>A doctor account provisioned via Add Doctor exists</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1. Open User Details for a doctor-role user</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>A linked doctor profile chip is shown with a working link through to that doctor's profile</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC-AM-008</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Admin Management</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Edit admin then save returns to the admin list</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>At least one user exists</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Edit Admin for a user
+2. Change a field
+3. Save</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Updated contact number</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Success message shown, then redirect to the Admin list (NOT the login page)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC-AM-009</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Admin Management</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Edit existing admin/staff details</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>At least one user exists</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. Open Edit Admin for a user
 2. Change name/contact/role
 3. Save</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Updated contact number</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Changes are saved and reflected in Admin list</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TC-AM-007</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TC-AM-010</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Admin Management</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Delete an admin/staff user</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>At least one non-self user exists</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. Go to Admin page
 2. Click delete on a user
 3. Confirm deletion</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>User is removed from the list and can no longer log in</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TC-AM-008</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Admin Management</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Role Management - view roles and permissions</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Logged in as admin</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Role Management page
-2. Review roles and assigned permissions</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Roles (admin, doctor, patient_manager, billing) and their permissions display correctly</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TC-AM-009</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Admin Management</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Role Management - update permissions for a role</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Logged in as admin</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a role
-2. Toggle a permission (e.g. manage_pharmacy)
-3. Save</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Toggle manage_pharmacy off</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Permission change is saved; user with that role loses/gains access accordingly</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TC-AM-010</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Admin Management</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Non-admin cannot access Admin page</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Logged in as non-admin role (e.g. billing)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as billing/doctor/patient_manager
-2. Try to navigate to /dashboard/admin</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>URL: /dashboard/admin</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Access is blocked/redirected; page/menu item not shown</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1590,27 +1589,28 @@
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-DM-001</t>
+          <t>TC-AM-011</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Doctor Management</t>
+          <t>Admin Management</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>View list of doctors</t>
+          <t>Role Management - view roles and permissions</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>At least one doctor exists</t>
+          <t>Logged in as admin</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Doctors page</t>
+          <t>1. Navigate to Role Management page
+2. Review roles and assigned permissions</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>List of doctors displays with name, specialization, contact details</t>
+          <t>Roles (admin, doctor, patient_manager, billing) and their permissions display correctly</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
@@ -1641,561 +1641,566 @@
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>TC-AM-012</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Admin Management</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Role Management - update permissions for a role</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as admin</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a role
+2. Tick/untick an action in a module row (e.g. Read - Pharmacy)
+3. Save</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>billing role: tick Read - Patients</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Permission change is saved to the Role record; unknown permission keys are rejected by the API</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TC-AM-013</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Admin Management</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Permission change requires affected user to re-login</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>A role's permissions were just changed</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1. Change a permission on a role
+2. With that role's user still logged in, retry the affected page
+3. Log that user out and back in
+4. Retry the page</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Add Read - Patients to billing role</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Change does NOT apply to the already-logged-in session (permissions are carried in the JWT/localStorage from login); after re-login the new permission applies</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TC-AM-014</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Admin Management</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Allow All covers read/write/edit for a module</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as admin</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a role
+2. Tick Allow All for a module only
+3. Save
+4. Log in as that role and exercise read + write + edit actions</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>pharmacy: Allow All only</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>All actions in that module are permitted by _allow_all alone; no need to also tick read/write/edit</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TC-AM-015</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Admin Management</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Non-admin cannot access Admin page</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as non-admin role (e.g. billing)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as billing/doctor/patient_manager
+2. Try to navigate to /dashboard/admin</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>URL: /dashboard/admin</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Access is blocked/redirected; page/menu item not shown</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TC-DM-001</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Management</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>View list of doctors</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>At least one doctor exists</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Doctors page</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>List of doctors displays with name, specialization, contact details</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>TC-DM-002</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Doctor Management</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Add a new doctor with valid details</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Logged in with permission</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. Go to Add Doctor page
 2. Fill in name, specialization, contact, fee, schedule
 3. Submit</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>name: Dr. Test, fee: 1500</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Doctor is created and appears in Doctor Management list</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>TC-DM-003</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Doctor Management</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Add doctor with missing required fields</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. Go to Add Doctor page
 2. Leave required fields blank
 3. Submit</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Blank fields</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Validation prevents submission with clear error messages</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>TC-DM-004</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Doctor Management</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Add doctor with invalid contact number format</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. Go to Add Doctor page
 2. Enter letters in contact field
 3. Submit</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>contact: abc123</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Field validation rejects non-numeric/invalid format</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>TC-DM-005</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Doctor Management</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>View single doctor profile</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Doctor record exists</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. From Doctors list, click on a doctor</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Doctor View page shows full profile details correctly</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>TC-DM-006</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Doctor Management</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Edit doctor details</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Doctor record exists</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. Open Doctor Edit page
 2. Update fee/specialization
 3. Save</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Updated fee: 2000</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Changes persist and reflect in Doctor list/profile</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>TC-DM-007</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Doctor Management</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Delete a doctor</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Doctor record exists with no active appointments</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. Go to Doctor Management
 2. Delete a doctor
 3. Confirm</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Doctor is removed from list; not selectable for new appointments</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TC-DM-008</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Doctor Management</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Doctor Portal - login as doctor and view assigned appointments</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Logged in as doctor role</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as a doctor
-2. Navigate to Doctor Home</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Doctor sees only their own appointments for the day/queue</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TC-DM-009</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Doctor Management</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Doctor Portal - open consultation for an appointment</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>An appointment assigned to the doctor exists</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1. From Doctor Home, click Consultation on an appointment</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Consultation page loads with patient details and prescription form</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TC-DM-010</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Doctor Management</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Doctor Portal - add prescription during consultation</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Consultation page open, medicines exist in inventory</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1. In Consultation, search medicine via autocomplete
-2. Select medicine, set quantity/dosage
-3. Save prescription</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Medicine: Paracetamol, qty: 10</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Prescription is saved with QUEUED status and appears in Pharmacy Dispense Queue</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TC-DM-011</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Doctor Management</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Non-doctor cannot access Doctor Portal</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Logged in as non-doctor role</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as admin/billing/patient_manager
-2. Try to navigate to /dashboard/doctor-home</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>URL: /dashboard/doctor-home</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Access blocked by ProtectedRoute (requiredPermission doctor_portal)</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TC-PM-001</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Patient Management</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>View list of registered patients</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>At least one patient exists</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Patients page</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Patient list displays with name, contact, registration details</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
@@ -2216,38 +2221,38 @@
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TC-PM-002</t>
+          <t>TC-DP-001</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Patient Management</t>
+          <t>Doctor Portal</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Search/filter patients by name or ID</t>
+          <t>Doctor sees today's queue and their upcoming appointments</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Multiple patients exist</t>
+          <t>Logged in as a doctor with appointments today and later</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1. Go to Patients page
-2. Enter search term</t>
+          <t>1. Log in as a doctor
+2. Open My Appointments</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Partial patient name</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>List filters correctly to matching patients</t>
+          <t>Two tables: Today (consultation queue) and Upcoming Appointments (after today, soonest first); stat tiles show Today's Total, Completed, Remaining and Upcoming</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2258,7 +2263,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
@@ -2268,1334 +2273,3508 @@
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>TC-DP-002</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Doctor sees only their own appointments</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Appointments exist for more than one doctor</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as doctor A
+2. Open My Appointments</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Only doctor A's appointments are listed; no other doctor's patients appear</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TC-DP-003</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Today's appointments are not duplicated in Upcoming</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>The doctor has appointments today and on later dates</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1. Open My Appointments
+2. Compare the two tables</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>No appointment appears in both tables; Upcoming starts from tomorrow so the day's workload is not double counted</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TC-DP-004</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Account with no linked doctor profile</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as a doctor-role user with no linked Doctor record</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1. Open My Appointments</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>A clear message explains no doctor profile is linked and to contact an admin, instead of an empty table</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-001</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Open a consultation from today's queue</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>An appointment assigned to the doctor exists for today</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1. From My Appointments, click Start Consultation</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Consultation page loads showing the patient header, clinical fields and the prescription method selector</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-002</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Patient header shows identifying and clinical context</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Patient record exists</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a consultation
+2. Review the header</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Shows patient name, patient ID, age, gender, contact, blood group, appointment date/time, service, doctor and appointment status</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-003</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Known allergies are highlighted</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>The patient has allergies recorded at the patient desk</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a consultation for that patient</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Allergies: Penicillin</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Allergies appear as a prominent warning callout in the patient header</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-004</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Save consultation as a draft</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Consultation page open</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1. Fill Chief Complaint, Symptoms, Examination, Diagnosis, Notes
+2. Click Save Consultation
+3. Reload the page</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Diagnosis: Tension headache</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Clinical fields are persisted and reloaded; the appointment is NOT completed and billing is not advanced</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-005</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Clinical notes are stored separately from the prescription</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>A consultation with notes but no medicines</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter a diagnosis and notes
+2. Choose No Prescription
+3. Complete the consultation</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>The clinical record is saved even though no prescription exists (notes are not lost with no medicines to dispense)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-006</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Type Prescription - medicine entry is shown</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Consultation page open, medicines in inventory</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1. Select Type Prescription</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>The medicine entry grid is shown with medicine search, quantity, dosage, frequency, duration and instructions</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-007</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Type Prescription - save and send to pharmacy</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Type Prescription selected</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1. Select a medicine and quantity
+2. Click Save Prescription</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Paracetamol, qty 10</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Prescription is saved, its items are QUEUED, and it appears in the Pharmacy Dispensing Queue</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-008</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Type Prescription - complete leaves the visit with pharmacy</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>A typed prescription has been saved</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Complete Consultation</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Appointment becomes Completed; the visit stays with the pharmacy and only becomes collectable in Billing after all items are dispensed</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-009</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Type Prescription - cannot complete with nothing saved</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Type Prescription selected, no medicines saved</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1. Select Type Prescription
+2. Click Complete Consultation without saving any medicine</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Completion is refused with a message to save the prescription or pick another method; nothing is billed and the appointment stays open</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-010</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Handwritten - medicine entry is hidden</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Consultation page open</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>1. Select Handwritten Prescription</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>The medicine grid is hidden and an explanation plus a confirmation checkbox is shown</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-011</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Handwritten - confirmation is required</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Handwritten Prescription selected, checkbox unticked</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1. Select Handwritten Prescription
+2. Click Complete Consultation without ticking the confirmation</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Completion is refused asking for confirmation that the paper prescription was given; appointment stays open and nothing is billed</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-012</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Handwritten - complete goes straight to billing</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Handwritten Prescription selected and confirmed</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>1. Tick the confirmation
+2. Click Complete Consultation</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Appointment becomes Completed; NO prescription is created; nothing appears in the pharmacy queue; the patient becomes collectable in Billing immediately</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-013</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Handwritten - reason is recorded for audit</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>A consultation was completed as handwritten</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1. Inspect the stored consultation record</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>prescriptionMode is stored as HANDWRITTEN with the confirmation timestamp, explaining why no pharmacy prescription exists</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-014</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>No Prescription - complete goes straight to billing</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Consultation page open</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1. Select No Prescription
+2. Click Complete Consultation</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>A note explains nothing goes to pharmacy; no prescription is created; prescriptionMode NONE stored; patient becomes collectable in Billing immediately</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-015</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Cannot switch to handwritten after queuing medicines</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>A typed prescription has already been saved for this visit</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1. Save a typed prescription
+2. Change the method to Handwritten or No Prescription
+3. Complete</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Completion is refused, because the pharmacy is already holding a prescription for this visit</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-016</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>A completed consultation cannot be completed twice</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>A consultation was already completed</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1. Reopen the consultation
+2. Attempt to complete it again</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Refused; the billing transition does not fire a second time and fields are read-only</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-017</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Previous consultations history</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>The patient has earlier completed consultations</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a consultation
+2. Review Previous Consultations</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Lists date, doctor, diagnosis, notes and what was prescribed for each earlier consultation</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-018</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Patient desk records stay separate from consultations</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>The patient has both registration vitals and past consultations</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a consultation
+2. Compare Previous Consultations with Patient Registration Records</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Two clearly separate panels: doctor-authored consultations, and vitals/history recorded at the patient desk</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-019</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Doctor is not exposed to internal billing states</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Consultation page open</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1. Review the whole page including after completion</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>No technical statuses (OPEN, PENDING_PHARMACY, READY_FOR_PAYMENT, CLOSED) are shown; only doctor-facing wording</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-020</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>SECURITY - prescription cannot be attributed to another doctor</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as doctor A; doctor B also exists</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. Start a consultation as doctor A
+2. Using browser devtools, alter the saved request to carry doctor B's id/name
+3. Save the prescription</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>doctorId/doctorName of doctor B</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>The stored prescription is attributed to doctor A (identity is derived server-side from the authenticated user; body values are ignored)</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-021</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>SECURITY - consultation cannot be attributed to another doctor</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as doctor A; doctor B also exists</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1. Alter the consultation save request to carry doctor B's id/name
+2. Save</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>doctorId/doctorName of doctor B</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>The consultation is recorded against doctor A, on every save, not just the first</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>TC-DC-022</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Consultation</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Non-doctor cannot record a consultation</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as a role without doctor_portal</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as billing/admin staff
+2. Attempt to save or complete a consultation via the API</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Request is refused by permission checks server-side, not only hidden in the UI</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>TC-DM-008</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Management</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Non-doctor cannot access Doctor Portal</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as non-doctor role</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as admin/billing/patient_manager
+2. Try to navigate to /dashboard/doctor-home</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>URL: /dashboard/doctor-home</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Access blocked by ProtectedRoute (requiredPermission doctor_portal)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>TC-PM-001</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Patient Management</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>View list of registered patients</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>At least one patient exists</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Patients page</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Patient list displays with name, contact, registration details</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>TC-PM-002</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Patient Management</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Search/filter patients by name or ID</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Multiple patients exist</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1. Go to Patients page
+2. Enter search term</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Partial patient name</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>List filters correctly to matching patients</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
           <t>TC-PM-003</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Patient Management</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Register a new patient with valid details</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Logged in with manage_patients permission</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. Go to Register Patient page
 2. Fill name, age, gender, contact, address
 3. Submit</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>name: Test Patient, age: 30</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Patient is created and appears in Patients list</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>TC-PM-004</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Patient Management</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Register patient with missing required fields</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. Go to Register Patient
 2. Leave required fields blank
 3. Submit</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Blank fields</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Form validation blocks submission, shows required errors</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>TC-PM-005</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Patient Management</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Register patient with invalid contact/NIC format</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. Go to Register Patient
 2. Enter invalid NIC/phone format
 3. Submit</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>NIC: 123, phone: abcd</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>Validation error shown for invalid format</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>TC-PM-006</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Patient Management</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>View patient profile</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Patient record exists</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. From Patients list, click View on a patient</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>View Patient page shows full record: history, appointments, billing summary</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>TC-PM-007</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Patient Management</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Edit patient details</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Patient record exists</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. Open Edit Patient page
 2. Update contact/address
 3. Save</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Updated phone number</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>Changes are saved and reflected in patient profile</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>TC-PM-008</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Patient Management</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Delete/deactivate a patient record</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Patient record exists</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. From Patients list, delete a patient
 2. Confirm</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Patient is removed/deactivated; historical records remain intact if applicable</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>TC-PM-009</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Patient Management</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Non-permitted role cannot access Patients module</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Logged in as role without manage_patients</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a restricted role
 2. Try to navigate to /dashboard/patients</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>URL: /dashboard/patients</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Access blocked/redirected by ProtectedRoute</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>TC-A-001</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Appointments</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>View list of appointments</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>At least one appointment exists</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>View appointments split into Upcoming and Past</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Appointments exist in both the future and the past</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Appointments page</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Appointments list shows patient, doctor, date/time, status</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Two separate tables: Upcoming Appointments (soonest first) and Past &amp; Closed Appointments (most recent first), each with its own count and pagination</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>TC-A-002</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Appointments</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled future appointment is not listed as Upcoming</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>A future-dated appointment has been cancelled</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1. Cancel a future appointment
+2. Reload the Appointments page</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Future date, status Cancelled</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>It appears under Past &amp; Closed, NOT under Upcoming (only still-Scheduled future bookings are upcoming)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-003</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Today's appointment with no time stays Upcoming</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>An appointment exists for today with the time field empty</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1. View the Appointments page</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Today's date, no time</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Still listed as Upcoming until the end of today rather than dropping into history</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-004</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Doctor column shows the current doctor</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>An appointment exists whose stored doctor name is blank or outdated</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1. View the Appointments page
+2. Check the Doctor column for that appointment</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>The live doctor is resolved from the appointment's doctor reference and shown with specialization; the column is not blank</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-005</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Deleted doctor is flagged on old appointments</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>An appointment references a doctor who has since been deleted</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1. View the Appointments page</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>The stored name is shown marked 'No longer registered' rather than presented as a current doctor</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-006</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Doctor dropdown excludes doctors on leave</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>One doctor has status On Leave, others Available/Busy</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>1. Open New Appointment
+2. Open the Select Doctor dropdown</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>One doctor set to On Leave</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>On Leave doctors are not offered; Available and Busy doctors are (Busy is transient and still bookable for a future date)</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-007</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Search the doctor dropdown by specialization</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Doctors with differing specializations exist</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>1. Open New Appointment
+2. Type a specialization into Select Doctor</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>e.g. 'General'</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Options are labelled 'Name - Specialization' and filter on the specialization text too</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-008</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Doctor list fails to load in New Appointment</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as a role with appointments access but no doctors read access</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>1. Open New Appointment</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>A clear error message is shown rather than a silently empty doctor dropdown</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-009</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Book a new appointment</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Patient and doctor records exist</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. Go to Add Appointment page
 2. Select patient, doctor, date/time
 3. Submit</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Existing patient + doctor, future date/time</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>Appointment is created; VisitSession auto-opened with Doctor Fee + Center Fee lines</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TC-A-003</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-010</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Appointments</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Book appointment with a past date/time</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. Go to Add Appointment
 2. Select a date/time in the past
 3. Submit</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Past date</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>Validation prevents booking a past-dated appointment</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TC-A-004</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-011</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Appointments</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Book overlapping/duplicate appointment for same doctor/slot</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>An appointment already exists for that doctor/slot</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to book same doctor at an already-booked time slot
 2. Submit</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Same doctor, same time slot</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>System warns or prevents double-booking for that slot</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TC-A-005</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-012</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Appointments</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Cancel an appointment</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>An OPEN appointment exists</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. From Appointments list, select an appointment
 2. Cancel it</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>Appointment status changes to canceled; linked VisitSession reflects CANCELED where applicable</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TC-A-006</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-013</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Appointments</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Reschedule an appointment</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>An existing appointment exists</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. Open an appointment
 2. Change date/time
 3. Save</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>New valid date/time</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>Appointment updates with new schedule, no duplicate created</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TC-A-007</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>TC-A-014</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Appointments</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Filter appointments by date or doctor</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Multiple appointments exist across dates/doctors</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. Go to Appointments page
 2. Apply date/doctor filter</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Specific date or doctor name</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>List filters correctly to matching appointments</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>TC-I-001</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>View medicine inventory list</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>At least one medicine exists</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Inventory page</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>Medicine list shows name, stock quantity, price, expiry</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>TC-I-002</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Add a new medicine with valid details</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Logged in with staff role</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. Go to Add Medicine page
 2. Fill name, quantity, price, expiry date
 3. Submit</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>name: Paracetamol 500mg, qty: 100</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>Medicine is added and appears in Inventory list</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>TC-I-003</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Add medicine with negative or zero stock quantity</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. Go to Add Medicine
 2. Enter negative/zero quantity
 3. Submit</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>qty: -5</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>Validation rejects invalid quantity</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>TC-I-004</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Add medicine with expiry date in the past</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. Go to Add Medicine
 2. Enter a past expiry date
 3. Submit</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Expiry: past date</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>Validation warns/rejects past expiry date</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>TC-I-005</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Edit medicine details / update stock</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medicine record exists</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. Open Edit Medicine
 2. Update stock quantity or price
 3. Save</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Updated qty: 150</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>Changes persist and reflect in Inventory list</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>TC-I-006</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Low stock warning indicator</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>A medicine's stock is below threshold</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. Set/observe a medicine with low stock
 2. View Inventory page</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Stock below reorder level</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>Low-stock medicines are visually flagged/highlighted</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>TC-I-007</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Delete a medicine from inventory</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medicine record exists, not referenced by pending prescriptions</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. From Inventory list, delete a medicine
 2. Confirm</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>Medicine is removed from list and no longer selectable in prescriptions</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>TC-PDQ-001</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Pharmacy Dispense Queue</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>View queued prescriptions</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>A prescription with QUEUED status exists</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in with manage_pharmacy permission
-2. Navigate to Pharmacy Dispense Queue</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>A prescription with QUEUED items exists</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in with pharmacy_read (or pharmacy_allow_all)
+2. Go to Pharmacy &gt; Dispensing Queue tab</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Queued prescriptions list shows patient, medicine, quantity, status</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Queued items list shows patient, doctor, medicine, dosage, prescribed/dispensed quantity and status</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>TC-PDQ-002</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Pharmacy Dispense Queue</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Doctor name shown in the queue is the real author</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>A typed prescription exists</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1. View the Dispensing Queue
+2. Compare the Doctor column against the doctor who wrote it</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Doctor shown is the authenticated doctor who saved the prescription, derived server-side (not a client-supplied value)</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-003</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacy Dispense Queue</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Read-only pharmacy user cannot dispense</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Logged in with pharmacy_read but NOT pharmacy_edit</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Dispensing Queue
+2. Attempt to dispense or reject an item</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Action is refused by the server with a permission error; no stock movement and no bill line</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-004</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacy Dispense Queue</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Dispense a prescription with sufficient stock</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>QUEUED prescription exists, stock available</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. Open a queued prescription
 2. Click Dispense
 3. Confirm</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Medicine with stock &gt;= prescribed qty</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>Prescription status changes to DISPENSED, stock decrements, bill line posted to VisitSession atomically</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TC-PDQ-003</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-005</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Pharmacy Dispense Queue</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Attempt to dispense with insufficient stock</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>QUEUED prescription exists, stock less than prescribed qty</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. Open a queued prescription where stock &lt; required qty
 2. Attempt to dispense</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Prescribed qty &gt; available stock</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>System blocks full dispense or offers PARTIAL fulfillment with clear message</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TC-PDQ-004</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-006</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Pharmacy Dispense Queue</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Partially dispense a prescription</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>QUEUED prescription exists, partial stock available</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1. Open queued prescription
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Partially dispense a prescription item</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>QUEUED item exists, partial stock available</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a queued item
 2. Dispense less than the prescribed quantity</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Dispense qty &lt; prescribed qty</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Prescription status becomes PARTIAL; correct stock decrement and bill line for dispensed amount only</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Prescribed 10, dispense 4</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Item becomes PARTIAL; stock decrements by 4 only; one MEDICATION bill line for 4; prescription stays PENDING</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-007</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacy Dispense Queue</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Partially dispensed item stays in the queue</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>An item was partially dispensed</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>1. After a partial dispense, return to the Dispensing Queue</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Prescribed 10, dispensed 4</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>The item is STILL listed (outstanding = QUEUED or PARTIAL) and shows the remaining quantity (6 remaining)</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-008</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacy Dispense Queue</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Dispense the remainder of a partial item</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>An item is PARTIAL with quantity still owed</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the PARTIAL item
+2. Confirm the pre-filled quantity</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Remaining 6</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Dialog defaults to the REMAINING quantity (6, not 10); dispense succeeds; item becomes DISPENSED; a second MEDICATION bill line is posted</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-009</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacy Dispense Queue</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Visit does not reach payment while an item is outstanding</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>An item is QUEUED or PARTIAL on the visit</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>1. Partially dispense an item
+2. Check the visit in Billing</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Prescribed 10, dispensed 4</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Visit stays at pharmacy and is NOT collectable in Billing until every item on the visit is resolved</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-010</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacy Dispense Queue</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Reject the remainder of a partial item</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>An item is PARTIAL and the rest cannot be supplied</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the PARTIAL item
+2. Reject with a reason</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Reason: out of stock</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Remainder is written off, no further stock movement or bill line; the visit can now progress to payment</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TC-PDQ-005</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-011</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Pharmacy Dispense Queue</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Cannot dispense an already completed item</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>An item is fully DISPENSED</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>1. Attempt to dispense the same item again</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Request is rejected; no extra stock movement and no duplicate bill line</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-012</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacy Dispense Queue</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Reject a prescription</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>QUEUED prescription exists</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. Open queued prescription
 2. Click Reject
@@ -3603,156 +5782,1564 @@
 4. Confirm</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>Prescription status changes to REJECTED; no stock/bill changes occur</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TC-PDQ-006</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-013</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Pharmacy Dispense Queue</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Non-permitted role cannot access Pharmacy page</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Logged in as role without manage_pharmacy</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as doctor/patient_manager without pharmacy permission
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as a role without pharmacy_read / pharmacy_allow_all</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as a doctor (no pharmacy permission)
 2. Try /dashboard/pharmacy</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>URL: /dashboard/pharmacy</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Access blocked/redirected by ProtectedRoute</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Access blocked/redirected by ProtectedRoute, and the API also refuses the underlying requests</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDQ-014</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacy Dispense Queue</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Concurrent dispensing cannot oversell stock</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>One medicine with limited stock; two pharmacy users</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>1. Set a medicine's stock to 10
+2. Have two users each dispense 7 of it at the same time</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Stock 10, two requests of 7</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Exactly one request succeeds; the other is refused for insufficient stock; final stock is 3 and never negative</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-001</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>External Rx is a separate workflow from the queue</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Logged in with pharmacy access</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>1. Go to Pharmacy
+2. Observe the tabs</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Two tabs: Dispensing Queue (our doctors' typed prescriptions) and External Rx (paper prescriptions from outside)</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-002</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Dispense a paper prescription for a registered patient</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Patient registered; medicines in stock</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>1. Open External Rx
+2. Keep Registered Patient selected and choose the patient
+3. Enter the outside doctor's name
+4. Add medicines and quantities
+5. Click Dispense</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Patient + 2 medicines</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Stock decreases for each medicine, MEDICATION bill lines are created, and the charges appear in Billing</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-003</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Medicines can only be chosen from inventory</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Open External Rx</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to type a medicine name that is not in inventory</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Free-text medicine name</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Only inventory medicines are selectable; arbitrary names cannot be entered</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-004</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Price comes from the current inventory price</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>A medicine with a known unit price</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>1. Add that medicine with a quantity
+2. Compare the line amount and total</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>qty 3 of a priced medicine</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Unit price and line amount match the current inventory price; the total is the sum of the lines</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-005</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Live stock is shown and shortages flagged</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>A medicine with limited stock</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>1. Select that medicine
+2. Enter a quantity above its stock</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>qty &gt; stock</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>In-stock figure is displayed and the quantity is visibly flagged before submitting</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-006</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Dispensing more than available stock is refused</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>A medicine with limited stock</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter a quantity greater than the stock
+2. Click Dispense</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>qty &gt; available stock</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Refused with a message naming the medicine and the available quantity; NO stock is moved and no bill line is created</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-007</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>A short line rolls back the whole prescription</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Two medicines, the second short of stock</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>1. Add medicine A with valid quantity and medicine B above its stock
+2. Click Dispense</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>A: valid, B: qty &gt; stock</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Whole request is refused; medicine A's stock is NOT reduced (all lines commit together or not at all) and no partial record is left</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-008</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Same medicine listed twice is refused</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Open External Rx</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1. Add the same medicine on two separate lines
+2. Click Dispense</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Same medicine x2</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Refused with a message to combine the quantities into one line</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-009</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Zero or fractional quantity is refused</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Open External Rx</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter a quantity of 0 or a decimal
+2. Click Dispense</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>qty: 0 / 2.5</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Refused; quantities must be whole numbers of at least 1</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-010</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>External Rx never enters the doctor prescription queue</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>An external prescription was dispensed</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>1. Dispense an external prescription
+2. Open the Dispensing Queue tab</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Nothing from the external prescription appears in the Dispensing Queue, and no doctor prescription record is fabricated for it</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-011</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Bill onto the patient's existing open visit</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>The patient has an open visit for today</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>1. Select the registered patient
+2. In Bill to, pick their open visit
+3. Dispense</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Existing open visit</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>MEDICATION lines are added to that visit alongside the existing fees, and the visit's status is left unchanged</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-012</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>External billing does not disturb the doctor workflow</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>The patient has a visit awaiting consultation or pharmacy</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>1. Bill an external prescription onto that visit
+2. Check the visit's progress</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>The visit continues through the normal consultation/pharmacy flow exactly as before; only the extra charge is added</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-013</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Standalone pharmacy bill when there is no visit</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>The patient has no open visit</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>1. Select the patient (Bill to = New pharmacy bill)
+2. Dispense</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>A separate pharmacy bill is created containing only medication charges (no doctor or centre fee) and is immediately collectable in Billing</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-014</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>GUEST - dispense to an unregistered walk-in</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Medicines in stock</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>1. Open External Rx
+2. Switch to Guest (not registered)
+3. Enter the guest's name and optionally a phone
+4. Add medicines
+5. Click Dispense</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Guest: Walk-in Visitor, 0770001111</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Sale succeeds, stock decreases, and a pharmacy bill is created for the guest and appears in Billing</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-015</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>GUEST - no patient record is created</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Note the patient count before testing</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>1. Dispense to a guest
+2. Open the Patients page and re-check the count/list</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Guest name</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>No new patient record is created; the patient registry and patient counts are unchanged</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-016</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>GUEST - bill is identifiable in Billing</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>A guest sale was dispensed</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Billing
+2. Locate the guest's bill</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>The bill is listed under the guest's name marked as a guest, so staff can tell it apart from a registered patient's bill</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-017</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>GUEST - name is required</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Guest mode selected</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>1. Switch to Guest
+2. Leave the name blank (or spaces only)
+3. Click Dispense</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Blank / '   '</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Refused asking for either a registered patient or a guest name; nothing is dispensed</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-018</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>GUEST - cannot be billed onto a real patient's visit</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>An open visit exists for a registered patient</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>1. Switch to Guest
+2. Attempt to submit with an existing visit as the bill target</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Guest + existing visitSessionId</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Refused; a guest sale can never be charged to another patient's visit</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-019</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>GUEST - no Bill to selector is offered</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Guest mode selected</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>1. Switch to Guest and review the form</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>The Bill to selector is hidden and the form explains a separate pharmacy bill will be created</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-020</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Switching between Registered and Guest clears the other identity</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Open External Rx</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>1. Select a registered patient
+2. Switch to Guest
+3. Switch back</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Only the relevant identity fields are used; the submitted sale matches the mode shown on screen</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-021</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>PERMISSION - read-only pharmacy user cannot dispense</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Logged in with pharmacy_read but NOT pharmacy_edit</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>1. Open External Rx
+2. Complete the form and click Dispense</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Server refuses with a permission error; no stock movement and no bill created (enforced server-side, not just hidden in the UI)</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-022</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>PERMISSION - role without pharmacy access is blocked</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as a doctor or other non-pharmacy role</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>1. Attempt to reach /dashboard/pharmacy and to call the external dispense API directly</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Both the page and the API are refused</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-023</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>PERMISSION - patient and medicine pickers need read access</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Logged in with pharmacy access but without patients read / inventory read</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>1. Open External Rx</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>A clear message explains which access is missing rather than showing empty dropdowns</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-024</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Dispensed-by is recorded from the logged-in user</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Logged in as a pharmacy user</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>1. Dispense an external prescription
+2. Inspect the stored record</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>The record shows the authenticated pharmacy user as dispenser; a name supplied in the request body is ignored</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-025</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Concurrent external dispensing cannot oversell</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>One medicine with limited stock; two pharmacy users</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>1. Set stock to 10
+2. Two users each dispense 7 of that medicine simultaneously</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Stock 10, two requests of 7</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Exactly one succeeds; the other is refused; final stock is 3 and never negative</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>TC-EP-026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>External Prescription</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Stock figures refresh after dispensing</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>An external prescription was just dispensed</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>1. Dispense, then re-open the medicine picker</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>The in-stock figures reflect the quantities just dispensed</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>TC-B-001</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>View billing list / visit sessions</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>At least one visit session exists</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Billing page</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>List shows patient, visit status (OPEN/PENDING_PHARMACY/READY_FOR_PAYMENT/CLOSED), total amount</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>TC-B-002</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>Create invoice for a visit ready for payment</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>VisitSession status is READY_FOR_PAYMENT</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. Open Billing for a patient
 2. Click Create Invoice
@@ -3760,210 +7347,210 @@
 4. Confirm</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>Invoice is generated with correct itemized totals matching all posted bill lines</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>TC-B-003</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>Attempt to create invoice while pharmacy items are still pending</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>VisitSession status is PENDING_PHARMACY</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. Open Billing for a visit still awaiting pharmacy dispense
 2. Attempt to create invoice</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>System prevents invoice creation or clearly flags pending pharmacy items until resolved</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>TC-B-004</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>Verify bill line accuracy (Doctor Fee + Center Fee + Pharmacy items)</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Appointment created and prescription dispensed</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. Create appointment (auto Doctor Fee + Center Fee)
 2. Dispense a prescription
 3. Open Billing for that visit</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>All bill lines appear correctly with accurate amounts and no duplication</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>TC-B-005</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>Close a visit session after payment</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Invoice created and payment recorded</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. Process payment for an invoice
 2. Verify visit session status</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>VisitSession status transitions to CLOSED; visit no longer editable</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>TC-P-001</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>Record a payment against an invoice</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>An unpaid invoice exists</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Payments page
 2. Select invoice
@@ -3971,772 +7558,772 @@
 4. Submit</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Full payment amount</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>Payment is recorded, invoice marked as paid, reflected in reports</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>TC-P-002</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>Record a partial payment</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>An unpaid invoice exists</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. Go to Payments
 2. Enter an amount less than total due
 3. Submit</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Partial amount</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>Payment recorded, remaining balance correctly tracked and displayed</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>TC-P-003</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>Record payment with amount exceeding invoice total</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>An unpaid invoice exists</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. Go to Payments
 2. Enter amount greater than invoice total
 3. Submit</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Amount &gt; total due</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>System rejects or flags overpayment with a validation message</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>TC-P-004</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>View payment history for a patient</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Patient has prior payments</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to patient's billing/payment history</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>All past payments display with date, amount, method, and reference</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>TC-R-001</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Reports</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>Generate daily revenue report</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Billing/payment data exists for the day</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Reports page
 2. Select 'Daily' and today's date
 3. Generate report</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Today's date</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>Report shows accurate totals matching recorded payments for the day</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>TC-R-002</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Reports</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>Generate report for a custom date range</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Billing data exists within range</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. Go to Reports
 2. Select a custom start/end date
 3. Generate</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Start: 2026-08-01, End: 2026-08-16</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>Report aggregates correctly across the selected range only</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>TC-R-003</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Reports</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>Generate report with no data in selected range</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>No transactions in a chosen future range</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. Go to Reports
 2. Select a date range with no activity
 3. Generate</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Future date range</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>Report shows empty state / zero totals without errors</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>TC-R-004</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Reports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>Export report (if supported)</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>A report has been generated</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. Generate any report
 2. Click Export/Download</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>Report downloads in expected format (PDF/CSV/Excel) with matching data</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>TC-S-001</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>View and update profile settings</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Logged in user</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Settings page
 2. Update name/contact/password
 3. Save</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Updated display name</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>Changes are saved and reflected across the app (e.g. Navbar)</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>TC-S-002</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>Change password with correct current password</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Logged in user</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. Go to Settings
 2. Enter current password + new password
 3. Save</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Valid current password + new password</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>Password updated; user can log in with new password</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>TC-S-003</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>Change password with incorrect current password</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Logged in user</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. Go to Settings
 2. Enter wrong current password + new password
 3. Save</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Wrong current password</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>Update rejected with clear error message</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>TC-N-001</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Sidebar shows only permitted menu items per role</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Logged in as various roles</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. Log in as each role (admin, doctor, billing, patient_manager)
 2. Observe Sidebar menu</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>Only menu items the role has permission for are visible</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>TC-N-002</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Notification bell displays relevant alerts</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>System has pending items (e.g. low stock, queued prescriptions)</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click Notification Bell icon</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>Relevant notifications display (e.g. low stock, pending pharmacy items)</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>TC-N-003</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>Unknown route redirects to login/home</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to a non-existent URL (e.g. /dashboard/xyz123)</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>URL: /dashboard/xyz123</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>App redirects to '/' (login) instead of showing a blank/broken page</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>TC-N-004</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Responsive layout on smaller screen widths</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. Resize browser to tablet/mobile width
 2. Navigate through dashboard pages</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>Layout adjusts (sidebar collapses/hides) without breaking content</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M81"/>
+  <autoFilter ref="A1:M150"/>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I150" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not Executed"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J150" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
